--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.18663242732482</v>
+        <v>7.017827769440283</v>
       </c>
       <c r="D2" t="n">
-        <v>42.10827838131581</v>
+        <v>6.842595236963819</v>
       </c>
       <c r="E2" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F2" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.26740416596569</v>
+        <v>2.968453176969425</v>
       </c>
       <c r="D3" t="n">
-        <v>18.13278241988419</v>
+        <v>2.94657714323118</v>
       </c>
       <c r="E3" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F3" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.497501033700203</v>
+        <v>1.055843917976283</v>
       </c>
       <c r="D4" t="n">
-        <v>7.157694835586571</v>
+        <v>1.163125410782818</v>
       </c>
       <c r="E4" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F4" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.81322323972126</v>
+        <v>8.744648776454705</v>
       </c>
       <c r="D5" t="n">
-        <v>54.12736719083944</v>
+        <v>8.795697168511408</v>
       </c>
       <c r="E5" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F5" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.33338598567951</v>
+        <v>7.85417522267292</v>
       </c>
       <c r="D6" t="n">
-        <v>48.60654398224152</v>
+        <v>7.898563397114247</v>
       </c>
       <c r="E6" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F6" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.84941387180321</v>
+        <v>4.200529754168022</v>
       </c>
       <c r="D7" t="n">
-        <v>26.85253326989629</v>
+        <v>4.363536656358147</v>
       </c>
       <c r="E7" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F7" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>63.23841690417104</v>
+        <v>10.27624274692779</v>
       </c>
       <c r="D8" t="n">
-        <v>22.17294536530588</v>
+        <v>3.603103621862206</v>
       </c>
       <c r="E8" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F8" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94525428477534</v>
+        <v>6.166103821275993</v>
       </c>
       <c r="D9" t="n">
-        <v>38.12384069053305</v>
+        <v>6.195124112211621</v>
       </c>
       <c r="E9" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F9" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.53387461430277</v>
+        <v>4.6367546248242</v>
       </c>
       <c r="D10" t="n">
-        <v>28.77967535416223</v>
+        <v>4.676697245051363</v>
       </c>
       <c r="E10" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F10" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9.332219158891714</v>
+        <v>1.516485613319904</v>
       </c>
       <c r="D11" t="n">
-        <v>9.64035015729592</v>
+        <v>1.566556900560587</v>
       </c>
       <c r="E11" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F11" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.31601746690026</v>
+        <v>6.876352838371292</v>
       </c>
       <c r="D12" t="n">
-        <v>26.07469091231648</v>
+        <v>4.237137273251427</v>
       </c>
       <c r="E12" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F12" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.18625367407199</v>
+        <v>5.067766222036698</v>
       </c>
       <c r="D13" t="n">
-        <v>31.19575419401977</v>
+        <v>5.069310056528213</v>
       </c>
       <c r="E13" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F13" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>17.09162158086549</v>
+        <v>2.777388506890643</v>
       </c>
       <c r="D14" t="n">
-        <v>17.02756004393314</v>
+        <v>2.766978507139135</v>
       </c>
       <c r="E14" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F14" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.22361274917191</v>
+        <v>6.373837071740435</v>
       </c>
       <c r="D15" t="n">
-        <v>38.92957395599214</v>
+        <v>6.326055767848723</v>
       </c>
       <c r="E15" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F15" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>18.7740268509819</v>
+        <v>3.050779363284558</v>
       </c>
       <c r="D16" t="n">
-        <v>71.80640754833863</v>
+        <v>11.66854122660503</v>
       </c>
       <c r="E16" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F16" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>51.02942824741102</v>
+        <v>8.29228209020429</v>
       </c>
       <c r="D17" t="n">
-        <v>50.76321512392354</v>
+        <v>8.249022457637576</v>
       </c>
       <c r="E17" t="n">
-        <v>16.14030167090027</v>
+        <v>2.622799021521295</v>
       </c>
       <c r="F17" t="n">
-        <v>16.89804309063542</v>
+        <v>2.745932002228255</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
